--- a/demo-output/DEMO - Otter Client 3 (Consultation)/AppointmentFlowSheet/DEMO - Otter Client 3 (Consultation) Appointment Flow Sheet.xlsx
+++ b/demo-output/DEMO - Otter Client 3 (Consultation)/AppointmentFlowSheet/DEMO - Otter Client 3 (Consultation) Appointment Flow Sheet.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="20">
   <si>
     <t>DATE</t>
   </si>
@@ -34,13 +34,13 @@
     <t xml:space="preserve">Virtual </t>
   </si>
   <si>
-    <t>July 11, 2026</t>
+    <t>July 29, 2026</t>
   </si>
   <si>
     <t xml:space="preserve">BM: </t>
   </si>
   <si>
-    <t>gallbladder pain — stones confirmed on ultrasound, surgeon wanted removal; hot flashes; sleep issues; energy issues; panic attacks</t>
+    <t>the gallbladder pain is back; I was getting pains in it; my liver enzymes were elevated; I'll just wake up in sheer panic for no reason</t>
   </si>
   <si>
     <t xml:space="preserve">LAYING 1 FOUNDATIONS:
@@ -54,12 +54,11 @@
 CNS:
 DENTAL: 
 HORMONAL: 
-ADDITIONAL:
-pituitary is a little bit offline
-HPA axis under stress
-gallbladder stress affecting digestion, bile production and detoxification
-adrenal cortex needs support to calm cortisol and fight-or-flight response
-body needs to reset its safety signal after chronic stress</t>
+ADDITIONAL: the pituitary is a little bit offline
+the central nervous system is clear
+we're finding some blocks
+the pituitary and hypothalamus worker like that
+the gallbladder is stuck out loud or showing a little bit of stress</t>
   </si>
   <si>
     <r>
@@ -263,13 +262,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Start Cytosine PTHPT
-Start Beta Plus
-Start Bio B Complex
-Start Catalyze the Core</t>
-  </si>
-  <si>
-    <t>SLEEP: some nights wake up in sheer panic</t>
+    <t>SLEEP: some nights where I'll just wake up in sheer panic</t>
   </si>
   <si>
     <t>WATER:</t>
@@ -278,7 +271,7 @@
     <t>CYCLE:</t>
   </si>
   <si>
-    <t>EXERCISE:</t>
+    <t>EXERCISE: when I was walking</t>
   </si>
   <si>
     <t>DIET:</t>
@@ -496,6 +489,9 @@
   </si>
   <si>
     <t>SLEEP:</t>
+  </si>
+  <si>
+    <t>EXERCISE:</t>
   </si>
 </sst>
 </file>
@@ -993,9 +989,7 @@
       <c r="E2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>12</v>
-      </c>
+      <c r="F2" s="13"/>
       <c r="G2" s="14"/>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
@@ -1040,7 +1034,7 @@
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="15"/>
       <c r="B4" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="17"/>
@@ -1090,7 +1084,7 @@
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="15"/>
       <c r="B6" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
@@ -1140,7 +1134,7 @@
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="15"/>
       <c r="B8" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
@@ -1190,7 +1184,7 @@
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="15"/>
       <c r="B10" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="17"/>
@@ -1240,7 +1234,7 @@
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="15"/>
       <c r="B12" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
@@ -1332,7 +1326,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>11</v>
@@ -1382,7 +1376,7 @@
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="15"/>
       <c r="B17" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -1432,7 +1426,7 @@
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="15"/>
       <c r="B19" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -1482,7 +1476,7 @@
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="15"/>
       <c r="B21" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
@@ -1532,7 +1526,7 @@
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="15"/>
       <c r="B23" s="9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
@@ -1582,7 +1576,7 @@
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="15"/>
       <c r="B25" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
@@ -1674,7 +1668,7 @@
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>11</v>
@@ -1724,7 +1718,7 @@
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="15"/>
       <c r="B30" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -1774,7 +1768,7 @@
     <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="15"/>
       <c r="B32" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
@@ -1824,7 +1818,7 @@
     <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="15"/>
       <c r="B34" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C34" s="17"/>
       <c r="D34" s="17"/>
@@ -1874,7 +1868,7 @@
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="15"/>
       <c r="B36" s="9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>
@@ -1924,7 +1918,7 @@
     <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" s="15"/>
       <c r="B38" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C38" s="17"/>
       <c r="D38" s="17"/>
@@ -2016,7 +2010,7 @@
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E41" s="12" t="s">
         <v>11</v>
@@ -2066,7 +2060,7 @@
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="15"/>
       <c r="B43" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C43" s="17"/>
       <c r="D43" s="17"/>
@@ -2116,7 +2110,7 @@
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" s="15"/>
       <c r="B45" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C45" s="17"/>
       <c r="D45" s="17"/>
@@ -2166,7 +2160,7 @@
     <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" s="15"/>
       <c r="B47" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C47" s="17"/>
       <c r="D47" s="17"/>
@@ -2216,7 +2210,7 @@
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49" s="15"/>
       <c r="B49" s="9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C49" s="17"/>
       <c r="D49" s="17"/>
@@ -2266,7 +2260,7 @@
     <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51" s="15"/>
       <c r="B51" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C51" s="17"/>
       <c r="D51" s="17"/>
@@ -2358,7 +2352,7 @@
       </c>
       <c r="C54" s="10"/>
       <c r="D54" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>11</v>
@@ -2408,7 +2402,7 @@
     <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56" s="15"/>
       <c r="B56" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C56" s="17"/>
       <c r="D56" s="17"/>
@@ -2458,7 +2452,7 @@
     <row r="58" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A58" s="15"/>
       <c r="B58" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C58" s="17"/>
       <c r="D58" s="17"/>
@@ -2508,7 +2502,7 @@
     <row r="60" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A60" s="15"/>
       <c r="B60" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C60" s="17"/>
       <c r="D60" s="17"/>
@@ -2558,7 +2552,7 @@
     <row r="62" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A62" s="15"/>
       <c r="B62" s="9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C62" s="17"/>
       <c r="D62" s="17"/>
@@ -2608,7 +2602,7 @@
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A64" s="15"/>
       <c r="B64" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C64" s="17"/>
       <c r="D64" s="17"/>
@@ -2700,7 +2694,7 @@
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E67" s="12" t="s">
         <v>11</v>
@@ -2750,7 +2744,7 @@
     <row r="69" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A69" s="15"/>
       <c r="B69" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C69" s="17"/>
       <c r="D69" s="17"/>
@@ -2800,7 +2794,7 @@
     <row r="71" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A71" s="15"/>
       <c r="B71" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C71" s="17"/>
       <c r="D71" s="17"/>
@@ -2850,7 +2844,7 @@
     <row r="73" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A73" s="15"/>
       <c r="B73" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C73" s="17"/>
       <c r="D73" s="17"/>
@@ -2900,7 +2894,7 @@
     <row r="75" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A75" s="15"/>
       <c r="B75" s="9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C75" s="17"/>
       <c r="D75" s="17"/>
@@ -2950,7 +2944,7 @@
     <row r="77" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A77" s="15"/>
       <c r="B77" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C77" s="17"/>
       <c r="D77" s="17"/>
@@ -3042,7 +3036,7 @@
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E80" s="12" t="s">
         <v>11</v>
@@ -3092,7 +3086,7 @@
     <row r="82" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A82" s="15"/>
       <c r="B82" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C82" s="17"/>
       <c r="D82" s="17"/>
@@ -3142,7 +3136,7 @@
     <row r="84" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A84" s="15"/>
       <c r="B84" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C84" s="17"/>
       <c r="D84" s="17"/>
@@ -3192,7 +3186,7 @@
     <row r="86" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A86" s="15"/>
       <c r="B86" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C86" s="17"/>
       <c r="D86" s="17"/>
@@ -3242,7 +3236,7 @@
     <row r="88" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A88" s="15"/>
       <c r="B88" s="9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C88" s="17"/>
       <c r="D88" s="17"/>
@@ -3292,7 +3286,7 @@
     <row r="90" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A90" s="15"/>
       <c r="B90" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C90" s="17"/>
       <c r="D90" s="17"/>
